--- a/output/indice_inmobiliario.xlsx
+++ b/output/indice_inmobiliario.xlsx
@@ -1357,7 +1357,7 @@
     <t>publicado = cifra del informe del mes; derivado_* = calculado desde la cifra y la variacion que publica otro informe; interpolado = hueco completado (alquiler: siguiendo el IPC nacional nivel general; venta: log-lineal).</t>
   </si>
   <si>
-    <t>3fc00cc 2026-10-07 17:48:35 -0300</t>
+    <t>3ff744a 2026-10-08 15:06:35 -0300</t>
   </si>
 </sst>
 </file>
